--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_245_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_245_R25.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7374</v>
+        <v>5.5238</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7693</v>
+        <v>2.918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.968</v>
+        <v>2.6058</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5231</v>
+        <v>4.28</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6698</v>
+        <v>2.1285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8532999999999999</v>
+        <v>2.1515</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4553</v>
+        <v>3.3226</v>
       </c>
       <c r="K2" t="n">
-        <v>2.756</v>
+        <v>2.2687</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6993</v>
+        <v>1.0539</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0678</v>
+        <v>0.9575</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0862</v>
+        <v>-0.1401</v>
       </c>
       <c r="O2" t="n">
-        <v>0.154</v>
+        <v>1.0976</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7736</v>
+        <v>1.3159</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4248</v>
+        <v>0.7551</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3488</v>
+        <v>0.5608</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1829</v>
+        <v>-0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1107</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9875</v>
+        <v>5.4873</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0792</v>
+        <v>4.7209</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9083</v>
+        <v>0.7664</v>
       </c>
       <c r="G3" t="n">
-        <v>4.28</v>
+        <v>3.5231</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1285</v>
+        <v>2.6698</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1515</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3226</v>
+        <v>3.4553</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2687</v>
+        <v>2.756</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0539</v>
+        <v>0.6993</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9575</v>
+        <v>0.0678</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1401</v>
+        <v>-0.0862</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0976</v>
+        <v>0.154</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7796</v>
+        <v>1.5235</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9164</v>
+        <v>1.3763</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8632</v>
+        <v>0.1472</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5361</v>
+        <v>-1.1829</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.1107</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0507</v>
+        <v>3.8312</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9888</v>
+        <v>2.6349</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0618</v>
+        <v>1.1963</v>
       </c>
       <c r="G4" t="n">
         <v>3.0253</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0975</v>
+        <v>-0.1219</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1661</v>
+        <v>-0.0316</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3917</v>
+        <v>2.8545</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3361</v>
+        <v>0.3284</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7278</v>
+        <v>2.5261</v>
       </c>
       <c r="G5" t="n">
         <v>0.9572000000000001</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2407</v>
+        <v>0.2221</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.955</v>
+        <v>-0.2906</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7143</v>
+        <v>0.5127</v>
       </c>
       <c r="V5" t="n">
         <v>0.2836</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9073</v>
+        <v>2.3455</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7367</v>
+        <v>2.2086</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1705</v>
+        <v>0.1369</v>
       </c>
       <c r="G6" t="n">
         <v>0.5124</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1233</v>
+        <v>-0.6851</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2271</v>
+        <v>-0.2607</v>
       </c>
       <c r="V6" t="n">
         <v>2.2862</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7786</v>
+        <v>1.5028</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1972</v>
+        <v>1.787</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4186</v>
+        <v>-0.2842</v>
       </c>
       <c r="G7" t="n">
         <v>1.0164</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5419</v>
+        <v>-0.8178</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7951</v>
+        <v>-0.6607</v>
       </c>
       <c r="V7" t="n">
         <v>1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5304</v>
+        <v>0.9919</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3486</v>
+        <v>1.5412</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8182</v>
+        <v>-0.5494</v>
       </c>
       <c r="G8" t="n">
         <v>2.3691</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2847</v>
+        <v>0.1768</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.094</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1906</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8181</v>
+        <v>-0.8517</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2538</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5643</v>
+        <v>-0.5979</v>
       </c>
       <c r="G9" t="n">
         <v>0.3667</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4863</v>
+        <v>-0.5199</v>
       </c>
       <c r="T9" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9304</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3457</v>
+        <v>-1.5976</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.153</v>
+        <v>-0.6065</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1928</v>
+        <v>-0.9911</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5036</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3962</v>
+        <v>0.3519</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2082</v>
+        <v>0.3383</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.188</v>
+        <v>0.0136</v>
       </c>
       <c r="V10" t="n">
         <v>-1.214</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5916</v>
+        <v>-2.3557</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0153</v>
+        <v>-1.7794</v>
       </c>
       <c r="F11" t="n">
         <v>-0.5763</v>
@@ -1312,10 +1312,10 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6133</v>
+        <v>-0.3774</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3145</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1265</v>
+        <v>-3.8741</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.398</v>
+        <v>-3.28</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7285</v>
+        <v>-0.5941</v>
       </c>
       <c r="G12" t="n">
         <v>-0.113</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6913</v>
+        <v>-1.4389</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0455</v>
+        <v>-0.9276</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6458</v>
+        <v>-0.5113</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2731</v>
+        <v>-5.256</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4206</v>
+        <v>-3.3026</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8526</v>
+        <v>-1.9534</v>
       </c>
       <c r="G13" t="n">
         <v>-2.126</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8457</v>
+        <v>-0.8285</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3229</v>
+        <v>-0.4237</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6778999999999999</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.2286</v>
+        <v>8.601899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.543000000000001</v>
+        <v>6.916699999999999</v>
       </c>
       <c r="F14" t="n">
         <v>1.6851</v>
@@ -1546,13 +1546,13 @@
         <v>12.7575</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5727</v>
+        <v>-1.1993</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6852000000000004</v>
+        <v>-0.3120999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8873</v>
+        <v>-0.8871</v>
       </c>
       <c r="V14" t="n">
         <v>-2.224</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5082</v>
+        <v>2.5975</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9314</v>
+        <v>2.7519</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4232</v>
+        <v>-0.1544</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5948</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0076</v>
+        <v>1.0969</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1429</v>
+        <v>0.9634</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1353</v>
+        <v>0.1336</v>
       </c>
       <c r="V15" t="n">
         <v>3.3273</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9001</v>
+        <v>1.3269</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1881</v>
+        <v>1.4804</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.288</v>
+        <v>-0.1535</v>
       </c>
       <c r="G16" t="n">
         <v>0.3333</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7266</v>
+        <v>0.1533</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9911</v>
+        <v>0.2833</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2645</v>
+        <v>-0.13</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9802</v>
+        <v>0.469</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5528</v>
+        <v>0.7271</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5726</v>
+        <v>-0.2581</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2319</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9436</v>
+        <v>0.4325</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7512</v>
+        <v>-0.0745</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1924</v>
+        <v>0.507</v>
       </c>
       <c r="V17" t="n">
         <v>0.8046</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.1503</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1616</v>
+        <v>1.3975</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2592</v>
+        <v>-1.2471</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6512</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7639</v>
+        <v>-0.516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8136</v>
+        <v>-0.5777</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0496</v>
+        <v>0.0617</v>
       </c>
       <c r="V18" t="n">
         <v>0.1577</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.368</v>
+        <v>-0.0022</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-1.0774</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.368</v>
+        <v>1.0752</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.368</v>
+        <v>-1.3729</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.3327</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.368</v>
+        <v>-0.0402</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3178</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.0701</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.3879</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.368</v>
+        <v>-1.6907</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.2626</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>-0.4281</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.749</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1577</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.1577</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7874</v>
+        <v>-0.368</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2236</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5638</v>
+        <v>-0.368</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1393</v>
+        <v>-0.368</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3602</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.221</v>
+        <v>-0.368</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2817</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.981</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6993</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8576</v>
+        <v>-0.368</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3792</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4783</v>
+        <v>-0.368</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1968</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6844</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4876</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3275</v>
+        <v>-0.7265</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0789</v>
+        <v>-0.8133</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7514</v>
+        <v>0.0868</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2435</v>
+        <v>-1.1393</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3228</v>
+        <v>-1.3602</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5663</v>
+        <v>0.221</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4483</v>
+        <v>-0.2817</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2436</v>
+        <v>-0.981</v>
       </c>
       <c r="L21" t="n">
-        <v>2.2048</v>
+        <v>0.6993</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2048</v>
+        <v>-0.8576</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5664</v>
+        <v>-0.3792</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3615</v>
+        <v>-0.4783</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4793</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.09180000000000001</v>
+        <v>0.2576</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6563</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5645</v>
+        <v>0.163</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3784</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5964</v>
+        <v>-0.9223</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.021</v>
+        <v>-1.3712</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4246</v>
+        <v>0.4489</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3729</v>
+        <v>2.2435</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3327</v>
+        <v>-0.3228</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0402</v>
+        <v>2.5663</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3178</v>
+        <v>3.4483</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0701</v>
+        <v>1.2436</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3879</v>
+        <v>2.2048</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6907</v>
+        <v>-1.2048</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2626</v>
+        <v>-1.5664</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4281</v>
+        <v>0.3615</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>-4.871</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8452</v>
+        <v>0.3134</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9471000000000001</v>
+        <v>0.0514</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1019</v>
+        <v>0.2621</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1577</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9863</v>
+        <v>-2.6324</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9113</v>
+        <v>-1.5574</v>
       </c>
       <c r="F23" t="n">
         <v>-1.075</v>
@@ -2248,10 +2248,10 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0668</v>
+        <v>0.4206</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1687</v>
+        <v>0.1852</v>
       </c>
       <c r="U23" t="n">
         <v>0.2355</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2363</v>
+        <v>-3.0676</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8308</v>
+        <v>-1.5949</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4054</v>
+        <v>-1.4726</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0263</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.21</v>
+        <v>-0.0413</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2173</v>
+        <v>-3.4804</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4534</v>
+        <v>-1.6277</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7639</v>
+        <v>-1.8527</v>
       </c>
       <c r="G25" t="n">
         <v>-3.077</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4577</v>
+        <v>0.2792</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.0468</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4147</v>
+        <v>0.326</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9145</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.228300000000001</v>
+        <v>-6.6557</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6851</v>
+        <v>-1.684999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.543100000000001</v>
+        <v>-4.970499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-10.8654</v>
@@ -2482,13 +2482,13 @@
         <v>11.5977</v>
       </c>
       <c r="S26" t="n">
-        <v>1.5728</v>
+        <v>3.1452</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8874</v>
+        <v>0.8874000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6853</v>
+        <v>2.2582</v>
       </c>
       <c r="V26" t="n">
         <v>2.223999999999999</v>
